--- a/LAHM/Rainier (UPS UPS UPS)/UPS metadata/LAHM_21.xlsx
+++ b/LAHM/Rainier (UPS UPS UPS)/UPS metadata/LAHM_21.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nesh/Library/CloudStorage/Dropbox/SNOW/LAHM/LAHM Sandbox/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nesh/Documents/Repositories/LAI_in_snow/LAHM/Rainier (UPS UPS UPS)/UPS metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D55CF431-79AE-F74B-ADB6-FED64AE1A849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF42818D-BA53-4547-BF79-D6D73C8D5009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="2000" windowWidth="26840" windowHeight="15000"/>
+    <workbookView xWindow="1580" yWindow="2000" windowWidth="20540" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LAHM_21" sheetId="1" r:id="rId1"/>
@@ -316,7 +316,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1152,7 +1152,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
